--- a/aq_files/0862.xlsx
+++ b/aq_files/0862.xlsx
@@ -1,98 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>What is the main goal of K-Means clustering?</t>
-  </si>
-  <si>
-    <t>What does the “K” represent in K-Means?</t>
-  </si>
-  <si>
-    <t>What is a centroid in K-Means?</t>
-  </si>
-  <si>
-    <t>How are initial centroids usually selected?</t>
-  </si>
-  <si>
-    <t>How is the distance between points and centroids calculated?</t>
-  </si>
-  <si>
-    <t>What happens in the assignment step of K-Means?</t>
-  </si>
-  <si>
-    <t>What happens in the update step of K-Means?</t>
-  </si>
-  <si>
-    <t>How does the algorithm know when to stop iterating?</t>
-  </si>
-  <si>
-    <t>How do you choose the optimal number of clusters?</t>
-  </si>
-  <si>
-    <t>What is the elbow method used for in K-Means?</t>
-  </si>
-  <si>
-    <t>How does feature scaling affect K-Means performance?</t>
-  </si>
-  <si>
-    <t>Can K-Means handle categorical variables directly?</t>
-  </si>
-  <si>
-    <t>How do you assign a new data point to an existing cluster?</t>
-  </si>
-  <si>
-    <t>How do outliers affect K-Means clustering?</t>
-  </si>
-  <si>
-    <t>How do you visualize clusters in 2D or 3D?</t>
-  </si>
-  <si>
-    <t>What is inertia in K-Means, and what does it indicate?</t>
-  </si>
-  <si>
-    <t>How can you improve K-Means results if clusters are poorly formed?</t>
-  </si>
-  <si>
-    <t>How do you implement K-Means in Python using scikit-learn?</t>
-  </si>
-  <si>
-    <t>How do you interpret cluster centroids after training?</t>
-  </si>
-  <si>
-    <t>How do you evaluate K-Means clustering performance without labels?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,793 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Row_ID,Full_Name,Address_Complete,Product_Hierarchy,Date_Time_Combined,Phone_Full,Email_Address,Location_Code,Order_Reference,Transaction_Data,Product_Attributes,City_State_Zip,Name_Title</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1,Smith, John,123 Main Street|Chicago|IL|60601|USA,Electronics|Computers|Laptops|MacBook Pro,2024-01-05 14:30:00,555-123-4567,john.smith@email.com,US-IL-CHI-001,ORD-1001-USA-2024,2024|01|001|SALE|COMPLETED,Color:Silver|Size:16-inch|RAM:16GB|Storage:512GB,Chicago,IL 60601,Mr. John A. Smith</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2,Davis, Emily,456 Oak Avenue|Boston|MA|02101|USA,Electronics|Accessories|Mice|Magic Mouse,2024-01-05 14:35:00,555-234-5678,emily.davis@email.com,US-MA-BOS-002,ORD-1002-USA-2024,2024|01|002|SALE|COMPLETED,Color:White|Type:Wireless|Connectivity:Bluetooth,Boston,MA 02101,Ms. Emily R. Davis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>3,Wilson, Robert,789 Pine Street|Toronto|ON|M5V2T6|CAN,Clothing|Mens|Denim|Designer Jeans,2024-01-06 09:15:00,555-345-6789,robert.wilson@email.ca,CA-ON-TOR-003,ORD-1003-CAN-2024,2024|01|003|SALE|PENDING,Color:Blue|Size:32x32|Material:Denim|Style:Slim,Toronto,ON M5V 2T6,Mr. Robert J. Wilson</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4,Johnson, Sarah,321 Elm Street|Austin|TX|78701|USA,Electronics|Monitors|4K|27-inch Monitor,2024-01-06 10:45:00,555-456-7890,sarah.johnson@email.com,US-TX-AUS-004,ORD-1004-USA-2024,2024|01|004|SALE|COMPLETED,Resolution:4K|Size:27-inch|Panel:IPS|Refresh:144Hz,Austin,TX 78701,Ms. Sarah M. Johnson</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>5,Brown, Michael,654 Maple Avenue|London|LDN|EC1A1BB|UK,Furniture|Chairs|Executive|Leather Chair,2024-01-07 11:20:00,555-567-8901,michael.brown@email.co.uk,UK-LDN-LON-005,ORD-1005-UK-2024,2024|01|005|SALE|SHIPPED,Material:Leather|Color:Black|Type:Executive|Adjustable:Yes,London,EC1A 1BB,Mr. Michael K. Brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6,Anderson, Lisa,987 Cedar Lane|Sydney|NSW|2000|AUS,Electronics|Keyboards|Mechanical|RGB Keyboard,2024-01-07 13:00:00,555-678-9012,lisa.anderson@email.com.au,AU-NSW-SYD-006,ORD-1006-AUS-2024,2024|01|006|SALE|COMPLETED,Type:Mechanical|Switch:Blue|RGB:Yes|Layout:Full,Sydney,NSW 2000,Ms. Lisa C. Anderson</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>7,Taylor, Robert,147 Birch Street|Los Angeles|CA|90001|USA,Clothing|Womens|Outerwear|Leather Jacket,2024-01-08 08:45:00,555-789-0123,robert.taylor@email.com,US-CA-LAX-007,ORD-1007-USA-2024,2024|01|007|SALE|PENDING,Color:Black|Material:Leather|Style:Biker|Size:L,Los Angeles,CA 90001,Mr. Robert D. Taylor</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8,Martinez, Jennifer,258 Spruce Avenue|Berlin|BE|10115|GER,Electronics|Tablets|iPad|iPad Pro,2024-01-08 09:30:00,555-890-1234,jennifer.martinez@email.de,DE-BE-BER-008,ORD-1008-GER-2024,2024|01|008|SALE|COMPLETED,Model:Pro|Size:12.9-inch|Storage:256GB|Cellular:Yes,Berlin,10115,Ms. Jennifer L. Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>9,Moore, Richard,369 Walnut Street|Paris|75|75001|FRA,Furniture|Lighting|Floor|Modern Lamp,2024-01-09 10:15:00,555-901-2345,richard.moore@email.fr,FR-75-PAR-009,ORD-1009-FRA-2024,2024|01|009|SALE|SHIPPED,Style:Modern|Color:Black|Height:60in|Dimmable:Yes,Paris,75001,Mr. Richard P. Moore</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>10,Wilson, Linda,741 Cherry Lane|Detroit|MI|48201|USA,Clothing|Mens|Footwear|Running Shoes,2024-01-09 14:20:00,555-012-3456,linda.wilson@email.com,US-MI-DET-010,ORD-1010-USA-2024,2024|01|010|SALE|RETURNED,Size:10|Color:Gray|Type:Running|Cushioning:High,Detroit,MI 48201,Ms. Linda S. Wilson</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>11,Davis, Patricia,852 Dogwood Drive|Vancouver|BC|V6B4Y8|CAN,Electronics|Computers|Gaming|Gaming Laptop,2024-01-10 11:00:00,555-123-4567,patricia.davis@email.ca,CA-BC-VAN-011,ORD-1011-CAN-2024,2024|01|011|SALE|COMPLETED,Processor:i7|RAM:16GB|GPU:RTX4060|Storage:1TB,Vancouver,V6B 4Y8,Ms. Patricia A. Davis</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12,Miller, Michael,951 Fir Lane|Manchester|MAN|M11AE|UK,Electronics|Audio|Headphones|Noise Cancelling,2024-01-10 15:30:00,555-234-5678,michael.miller@email.co.uk,UK-MAN-MAN-012,ORD-1012-UK-2024,2024|01|012|SALE|COMPLETED,Type:Over-ear|NoiseCancelling:Yes|Wireless:Yes|Battery:30hr,Manchester,M1 1AE,Mr. Michael T. Miller</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>13,Thomas, Jessica,753 Poplar Avenue|San Diego|CA|92101|USA,Clothing|Womens|Outerwear|Wool Coat,2024-01-11 09:45:00,555-345-6789,jessica.thomas@email.com,US-CA-SAN-013,ORD-1013-USA-2024,2024|01|013|SALE|PENDING,Color:Camel|Size:M|Material:Wool|Style:Classic,San Diego,CA 92101,Ms. Jessica R. Thomas</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>14,White, Sarah,159 Cypress Court|Melbourne|VIC|3000|AUS,Furniture|Storage|Bookshelf|Oak Bookshelf,2024-01-11 12:15:00,555-456-7890,sarah.white@email.com.au,AU-VIC-MEL-014,ORD-1014-AUS-2024,2024|01|014|SALE|SHIPPED,Material:Oak|Shelves:5|Height:72in|Width:36in,Melbourne,VIC 3000,Ms. Sarah K. White</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>15,Walker, James,357 Willow Drive|Munich|BY|80331|GER,Electronics|Phones|Smartphone|iPhone Pro,2024-01-12 10:00:00,555-567-8901,james.walker@email.de,DE-BY-MUC-015,ORD-1015-GER-2024,2024|01|015|SALE|COMPLETED,Model:15 Pro|Storage:256GB|Color:Black|5G:Yes,Munich,80331,Mr. James R. Walker</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>16,Anderson, Thomas,951 Magnolia Road|Lyon|69|69001|FRA,Clothing|Mens|Shirts|Dress Shirt,2024-01-12 13:45:00,555-678-9012,thomas.anderson@email.fr,FR-69-LYO-016,ORD-1016-FRA-2024,2024|01|016|SALE|COMPLETED,Color:White|Size:L|Material:Cotton|Style:Formal,Lyon,69001,Mr. Thomas P. Anderson</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>17,Jackson, Charles,753 Ash Street|Portland|OR|97201|USA,Electronics|Storage|SSD|External SSD,2024-01-13 08:30:00,555-789-0123,charles.jackson@email.com,US-OR-PDX-017,ORD-1017-USA-2024,2024|01|017|SALE|COMPLETED,Capacity:1TB|Type:SSD|Interface:USB-C|Speed:1000MB/s,Portland,OR 97201,Mr. Charles D. Jackson</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>18,Harris, Daniel,159 Beech Court|Calgary|AB|T2P1J9|CAN,Clothing|Womens|Tops|Cotton Hoodie,2024-01-13 16:20:00,555-890-1234,daniel.harris@email.ca,CA-AB-CGY-018,ORD-1018-CAN-2024,2024|01|018|SALE|RETURNED,Color:Gray|Size:M|Material:Cotton|Style:Hoodie,Calgary,T2P 1J9,Mr. Daniel S. Harris</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>19,King, Edward,357 Cedar Avenue|Birmingham|WMD|B11BB|UK,Furniture|Desks|Gaming|RGB Gaming Desk,2024-01-14 11:30:00,555-901-2345,edward.king@email.co.uk,UK-WMD-BIR-019,ORD-1019-UK-2024,2024|01|019|SALE|SHIPPED,Color:Black|RGB:Yes|Size:60in|HeightAdjustable:Yes,Birmingham,B1 1BB,Mr. Edward M. King</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>20,Young, Kevin,753 Palm Avenue|Seattle|WA|98101|USA,Electronics|Accessories|Webcam|4K Webcam,2024-01-14 14:15:00,555-012-3456,kevin.young@email.com,US-WA-SEA-020,ORD-1020-USA-2024,2024|01|020|SALE|COMPLETED,Resolution:4K|FrameRate:60fps|AutoFocus:Yes|Mic:Yes,Seattle,WA 98101,Mr. Kevin L. Young</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>21,Lopez, George,951 Elm Drive|Brisbane|QLD|4000|AUS,Electronics|Docks|Docking|Thunderbolt Dock,2024-02-01 09:00:00,555-123-4567,george.lopez@email.com.au,AU-QLD-BNE-021,ORD-1021-AUS-2024,2024|02|021|SALE|COMPLETED,Ports:Thunderbolt4|HDMI:2|USB:4|Ethernet:Yes,Brisbane,QLD 4000,Mr. George R. Lopez</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>22,Allen, Nancy,753 Oak Court|Hamburg|HH|20095|GER,Clothing|Mens|Outerwear|Winter Parka,2024-02-01 10:45:00,555-234-5678,nancy.allen@email.de,DE-HH-HAM-022,ORD-1022-GER-2024,2024|02|022|SALE|PENDING,Color:Black|Size:XL|Material:Down|Waterproof:Yes,Hamburg,20095,Ms. Nancy K. Allen</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>23,Wright, Donna,159 Pine Street|Toulouse|31|31000|FRA,Furniture|Desks|Office|Office Desk,2024-02-02 13:30:00,555-345-6789,donna.wright@email.fr,FR-31-TLS-023,ORD-1023-FRA-2024,2024|02|023|SALE|SHIPPED,Material:Wood|Color:Walnut|Size:60x30|Drawers:3,Toulouse,31000,Ms. Donna M. Wright</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>24,Carter, Kimberly,357 Spruce Lane|Denver|CO|80201|USA,Electronics|Cables|Hub|USB-C Hub,2024-02-02 15:20:00,555-456-7890,kimberly.carter@email.com,US-CO-DEN-024,ORD-1024-USA-2024,2024|02|024|SALE|COMPLETED,Ports:7|USB-C:2|HDMI:1|SDCard:Yes,Denver,CO 80201,Ms. Kimberly S. Carter</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>25,Stewart, Mark,951 Walnut Avenue|Edmonton|AB|T5J0A9|CAN,Clothing|Mens|Blazers|Casual Blazer,2024-02-03 08:15:00,555-567-8901,mark.stewart@email.ca,CA-AB-EDM-025,ORD-1025-CAN-2024,2024|02|025|SALE|PENDING,Color:Navy|Size:42R|Material:Wool|Style:SingleBreasted,Edmonton,T5J 0A9,Mr. Mark T. Stewart</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Full_Name' column into 'Last_Name' and 'First_Name' columns using comma delimiter. How many columns are created?</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Address_Complete' column by pipe delimiter '|' into separate columns for Street, City, State, Zip, Country.</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Product_Hierarchy' column by pipe delimiter into 'Category', 'SubCategory', 'Type', 'Product_Name' columns.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Date_Time_Combined' column by space delimiter into 'Date' and 'Time' columns.</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Phone_Full' column by hyphen '-' into 'Area_Code', 'Prefix', 'Line_Number' columns.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Email_Address' column by '@' delimiter into 'Username' and 'Domain' columns.</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Location_Code' column by hyphen '-' into 'Country', 'State', 'City', 'Code' columns.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Order_Reference' column by hyphen into 'Order_Prefix', 'Order_Number', 'Country_Code', 'Year' columns.</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Transaction_Data' column by pipe delimiter into 'Year', 'Month', 'Sequence', 'Type', 'Status' columns.</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Product_Attributes' column by pipe delimiter into multiple attribute columns. Then split each attribute by colon.</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'City_State_Zip' column by space into 'City' and 'State_Zip' first, then split 'State_Zip' by space into 'State' and 'Zip'.</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Name_Title' column into 'Title', 'First_Name', 'Middle_Initial', 'Last_Name' columns using space delimiter.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Merge the 'First_Name' and 'Last_Name' columns (from previous split) back into a single 'Full_Name_Reconstructed' column with space separator.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Merge the 'Street', 'City', 'State', 'Zip' columns back into a single 'Full_Address' column with comma and space separators.</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Merge the 'Category', 'SubCategory', 'Type', 'Product_Name' columns into a single 'Product_Full' column with ' &gt; ' separator.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Product_Attributes' column by pipe, then merge specific attributes back with different separator.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Address_Complete' column into rows (not columns) for each component. This creates multiple rows per address.</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Phone_Full' column by hyphen, then merge back with a different separator like '.' or space.</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Location_Code' by hyphen, then merge 'Country' and 'State' with '-' and 'City' and 'Code' with '-' separately.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Splitting and Merging Columns</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Split the 'Date_Time_Combined' into Date and Time, then merge Date with 'Order_Reference' to create a composite key.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>